--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,10 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>SALOMON</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1060,10 +1051,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1072,29 +1063,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920050</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
@@ -82,13 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>EDER</t>
   </si>
 </sst>
 </file>
@@ -684,16 +684,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -707,16 +710,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.34999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -730,16 +736,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -753,16 +762,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -776,16 +788,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -799,16 +814,19 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H7">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -864,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -890,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>97.67</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -916,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -942,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -968,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>91.89</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -994,13 +1012,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>92.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -1045,7 +1063,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920049</v>
+        <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1060,7 +1078,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>EDER</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1061,29 +1052,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920006</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
@@ -873,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,7 +908,7 @@
         <v>95.34999999999999</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -925,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>84.62</v>
+        <v>82.05</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -951,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -977,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>86.48999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,7 +1012,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>GLORIA</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1052,6 +1070,52 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920159</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920386</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
